--- a/livrables/km_restants_sous_grande_vitesse.xlsx
+++ b/livrables/km_restants_sous_grande_vitesse.xlsx
@@ -430,7 +430,7 @@
   <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
@@ -497,7 +497,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -569,7 +569,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -605,7 +605,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -641,7 +641,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -677,7 +677,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -713,7 +713,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -749,7 +749,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -785,7 +785,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -821,7 +821,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -857,7 +857,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -893,7 +893,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -929,7 +929,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -965,7 +965,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1001,7 +1001,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1037,7 +1037,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1073,7 +1073,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1109,7 +1109,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1145,7 +1145,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1181,7 +1181,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1217,7 +1217,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1253,7 +1253,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1289,7 +1289,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1325,7 +1325,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1361,7 +1361,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1397,7 +1397,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1433,7 +1433,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1469,7 +1469,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1505,7 +1505,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1541,7 +1541,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1577,7 +1577,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1613,7 +1613,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1649,7 +1649,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1685,7 +1685,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1721,7 +1721,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1757,7 +1757,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1793,7 +1793,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1829,7 +1829,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1865,7 +1865,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1901,7 +1901,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1937,7 +1937,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1973,7 +1973,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2009,7 +2009,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -2045,7 +2045,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2081,7 +2081,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -2117,7 +2117,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2153,7 +2153,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -2189,7 +2189,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2225,7 +2225,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -2261,7 +2261,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2297,7 +2297,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -2333,7 +2333,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2369,7 +2369,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -2405,7 +2405,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2441,7 +2441,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -2477,7 +2477,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2513,7 +2513,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -2549,7 +2549,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -2585,7 +2585,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -2621,7 +2621,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="B61" t="n">

--- a/livrables/km_restants_sous_grande_vitesse.xlsx
+++ b/livrables/km_restants_sous_grande_vitesse.xlsx
@@ -512,16 +512,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>88</v>
+        <v>99.2</v>
       </c>
       <c r="F2" t="n">
-        <v>54.7</v>
+        <v>61.6</v>
       </c>
       <c r="G2" t="n">
-        <v>32.6</v>
+        <v>36.8</v>
       </c>
       <c r="H2" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -548,13 +548,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>99.2</v>
+        <v>106.3</v>
       </c>
       <c r="F3" t="n">
-        <v>61.7</v>
+        <v>66</v>
       </c>
       <c r="G3" t="n">
-        <v>53.7</v>
+        <v>57.5</v>
       </c>
       <c r="H3" t="n">
         <v>17</v>
@@ -584,16 +584,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>98.40000000000001</v>
+        <v>133.9</v>
       </c>
       <c r="F4" t="n">
-        <v>61.2</v>
+        <v>83.2</v>
       </c>
       <c r="G4" t="n">
-        <v>22.2</v>
+        <v>30.2</v>
       </c>
       <c r="H4" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -620,16 +620,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>72.5</v>
+        <v>111.8</v>
       </c>
       <c r="F5" t="n">
-        <v>45</v>
+        <v>69.5</v>
       </c>
       <c r="G5" t="n">
-        <v>13.5</v>
+        <v>20.9</v>
       </c>
       <c r="H5" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -656,16 +656,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>116.8</v>
+        <v>119.5</v>
       </c>
       <c r="F6" t="n">
-        <v>72.59999999999999</v>
+        <v>74.3</v>
       </c>
       <c r="G6" t="n">
-        <v>43.3</v>
+        <v>44.3</v>
       </c>
       <c r="H6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I6" t="n">
         <v>0.82</v>
@@ -692,16 +692,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105.9</v>
+        <v>107.2</v>
       </c>
       <c r="F7" t="n">
-        <v>65.8</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>57.3</v>
+        <v>58</v>
       </c>
       <c r="H7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I7" t="n">
         <v>0.82</v>
@@ -728,16 +728,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>148</v>
+        <v>154.3</v>
       </c>
       <c r="F8" t="n">
-        <v>91.90000000000001</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>33.4</v>
+        <v>34.9</v>
       </c>
       <c r="H8" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I8" t="n">
         <v>0.82</v>
@@ -764,16 +764,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>123.8</v>
+        <v>130.1</v>
       </c>
       <c r="F9" t="n">
-        <v>76.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="G9" t="n">
-        <v>23.1</v>
+        <v>24.3</v>
       </c>
       <c r="H9" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="I9" t="n">
         <v>0.82</v>
@@ -1217,7 +1217,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>recommande</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1232,16 +1232,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>46</v>
+        <v>67.5</v>
       </c>
       <c r="F22" t="n">
-        <v>28.6</v>
+        <v>41.9</v>
       </c>
       <c r="G22" t="n">
-        <v>17.1</v>
+        <v>25</v>
       </c>
       <c r="H22" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="I22" t="n">
         <v>1.59</v>
@@ -1253,7 +1253,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>recommande</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1268,16 +1268,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>19.3</v>
+        <v>29.9</v>
       </c>
       <c r="F23" t="n">
-        <v>12</v>
+        <v>18.6</v>
       </c>
       <c r="G23" t="n">
-        <v>10.4</v>
+        <v>16.2</v>
       </c>
       <c r="H23" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I23" t="n">
         <v>1.59</v>
@@ -1289,7 +1289,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>recommande</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1304,16 +1304,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>15.3</v>
+        <v>68.3</v>
       </c>
       <c r="F24" t="n">
-        <v>9.5</v>
+        <v>42.4</v>
       </c>
       <c r="G24" t="n">
-        <v>3.5</v>
+        <v>15.4</v>
       </c>
       <c r="H24" t="n">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="I24" t="n">
         <v>1.59</v>
@@ -1325,7 +1325,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>recommande</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1340,16 +1340,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>13.9</v>
+        <v>69.8</v>
       </c>
       <c r="F25" t="n">
-        <v>8.6</v>
+        <v>43.4</v>
       </c>
       <c r="G25" t="n">
-        <v>2.6</v>
+        <v>13</v>
       </c>
       <c r="H25" t="n">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="I25" t="n">
         <v>1.59</v>
@@ -1361,7 +1361,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>recommande</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1376,16 +1376,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>72.3</v>
+        <v>89.7</v>
       </c>
       <c r="F26" t="n">
-        <v>44.9</v>
+        <v>55.7</v>
       </c>
       <c r="G26" t="n">
-        <v>26.8</v>
+        <v>33.3</v>
       </c>
       <c r="H26" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="I26" t="n">
         <v>1.3</v>
@@ -1397,7 +1397,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>recommande</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1412,16 +1412,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>96</v>
+        <v>105.3</v>
       </c>
       <c r="F27" t="n">
-        <v>59.6</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>51.9</v>
+        <v>57</v>
       </c>
       <c r="H27" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I27" t="n">
         <v>1.3</v>
@@ -1433,7 +1433,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>recommande</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1448,16 +1448,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>35.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>22.2</v>
+        <v>52.7</v>
       </c>
       <c r="G28" t="n">
-        <v>8.1</v>
+        <v>19.2</v>
       </c>
       <c r="H28" t="n">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="I28" t="n">
         <v>1.3</v>
@@ -1469,7 +1469,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>recommande</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1484,16 +1484,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>29.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>18.4</v>
+        <v>52</v>
       </c>
       <c r="G29" t="n">
-        <v>5.5</v>
+        <v>15.6</v>
       </c>
       <c r="H29" t="n">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="I29" t="n">
         <v>1.3</v>
@@ -1505,7 +1505,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>recommande</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>81</v>
+        <v>93.2</v>
       </c>
       <c r="F30" t="n">
-        <v>50.3</v>
+        <v>57.9</v>
       </c>
       <c r="G30" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="H30" t="n">
         <v>30</v>
-      </c>
-      <c r="H30" t="n">
-        <v>24</v>
       </c>
       <c r="I30" t="n">
         <v>1.02</v>
@@ -1541,7 +1541,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>recommande</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1556,13 +1556,13 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>97.09999999999999</v>
+        <v>105.3</v>
       </c>
       <c r="F31" t="n">
-        <v>60.4</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>52.6</v>
+        <v>57</v>
       </c>
       <c r="H31" t="n">
         <v>17</v>
@@ -1577,7 +1577,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>recommande</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>62.6</v>
+        <v>104.4</v>
       </c>
       <c r="F32" t="n">
-        <v>38.9</v>
+        <v>64.8</v>
       </c>
       <c r="G32" t="n">
-        <v>14.1</v>
+        <v>23.6</v>
       </c>
       <c r="H32" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="I32" t="n">
         <v>1.02</v>
@@ -1613,7 +1613,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>recommande</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1628,16 +1628,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>60.5</v>
+        <v>105.2</v>
       </c>
       <c r="F33" t="n">
-        <v>37.6</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>11.3</v>
+        <v>19.6</v>
       </c>
       <c r="H33" t="n">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="I33" t="n">
         <v>1.02</v>
@@ -1649,7 +1649,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>recommande</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1685,7 +1685,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>recommande</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1721,7 +1721,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>recommande</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1757,7 +1757,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>recommande</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1793,7 +1793,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>recommande</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1829,7 +1829,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>recommande</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1865,7 +1865,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>recommande</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1901,7 +1901,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>recommande</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1952,16 +1952,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>19.2</v>
+        <v>33.1</v>
       </c>
       <c r="F42" t="n">
-        <v>11.9</v>
+        <v>20.6</v>
       </c>
       <c r="G42" t="n">
-        <v>7.1</v>
+        <v>12.3</v>
       </c>
       <c r="H42" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="I42" t="n">
         <v>2.26</v>
@@ -1988,16 +1988,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>9</v>
+        <v>16.3</v>
       </c>
       <c r="F43" t="n">
-        <v>5.6</v>
+        <v>10.1</v>
       </c>
       <c r="G43" t="n">
-        <v>4.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H43" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I43" t="n">
         <v>2.26</v>
@@ -2024,16 +2024,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>9</v>
+        <v>23.6</v>
       </c>
       <c r="F44" t="n">
-        <v>5.6</v>
+        <v>14.7</v>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>5.3</v>
       </c>
       <c r="H44" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="I44" t="n">
         <v>2.26</v>
@@ -2060,16 +2060,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>8.1</v>
+        <v>19.6</v>
       </c>
       <c r="F45" t="n">
-        <v>5.1</v>
+        <v>12.2</v>
       </c>
       <c r="G45" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="H45" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I45" t="n">
         <v>2.26</v>
@@ -2096,16 +2096,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>24.6</v>
+        <v>43.7</v>
       </c>
       <c r="F46" t="n">
-        <v>15.3</v>
+        <v>27.2</v>
       </c>
       <c r="G46" t="n">
-        <v>9.1</v>
+        <v>16.2</v>
       </c>
       <c r="H46" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="I46" t="n">
         <v>1.85</v>
@@ -2132,16 +2132,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>16.7</v>
+        <v>26.3</v>
       </c>
       <c r="F47" t="n">
-        <v>10.4</v>
+        <v>16.3</v>
       </c>
       <c r="G47" t="n">
-        <v>9.1</v>
+        <v>14.2</v>
       </c>
       <c r="H47" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="I47" t="n">
         <v>1.85</v>
@@ -2168,16 +2168,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>12.2</v>
+        <v>52.1</v>
       </c>
       <c r="F48" t="n">
-        <v>7.6</v>
+        <v>32.4</v>
       </c>
       <c r="G48" t="n">
-        <v>2.8</v>
+        <v>11.8</v>
       </c>
       <c r="H48" t="n">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="I48" t="n">
         <v>1.85</v>
@@ -2204,16 +2204,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>11.8</v>
+        <v>53</v>
       </c>
       <c r="F49" t="n">
-        <v>7.3</v>
+        <v>33</v>
       </c>
       <c r="G49" t="n">
-        <v>2.2</v>
+        <v>9.9</v>
       </c>
       <c r="H49" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="I49" t="n">
         <v>1.85</v>
@@ -2240,16 +2240,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>68.7</v>
+        <v>88.8</v>
       </c>
       <c r="F50" t="n">
-        <v>42.7</v>
+        <v>55.2</v>
       </c>
       <c r="G50" t="n">
-        <v>25.5</v>
+        <v>32.9</v>
       </c>
       <c r="H50" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I50" t="n">
         <v>1.45</v>
@@ -2276,16 +2276,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>92.7</v>
+        <v>103</v>
       </c>
       <c r="F51" t="n">
-        <v>57.6</v>
+        <v>64</v>
       </c>
       <c r="G51" t="n">
-        <v>50.2</v>
+        <v>55.8</v>
       </c>
       <c r="H51" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I51" t="n">
         <v>1.45</v>
@@ -2312,16 +2312,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>19.9</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F52" t="n">
-        <v>12.3</v>
+        <v>45</v>
       </c>
       <c r="G52" t="n">
-        <v>4.5</v>
+        <v>16.4</v>
       </c>
       <c r="H52" t="n">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="I52" t="n">
         <v>1.45</v>
@@ -2348,16 +2348,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>18.1</v>
+        <v>73.2</v>
       </c>
       <c r="F53" t="n">
-        <v>11.3</v>
+        <v>45.5</v>
       </c>
       <c r="G53" t="n">
-        <v>3.4</v>
+        <v>13.7</v>
       </c>
       <c r="H53" t="n">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="I53" t="n">
         <v>1.45</v>
@@ -2384,16 +2384,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>110.8</v>
+        <v>118.6</v>
       </c>
       <c r="F54" t="n">
-        <v>68.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="G54" t="n">
-        <v>41.1</v>
+        <v>44</v>
       </c>
       <c r="H54" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I54" t="n">
         <v>0.93</v>
@@ -2420,16 +2420,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>102.3</v>
+        <v>107.2</v>
       </c>
       <c r="F55" t="n">
-        <v>63.6</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>55.4</v>
+        <v>58</v>
       </c>
       <c r="H55" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I55" t="n">
         <v>0.93</v>
@@ -2456,16 +2456,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>123.8</v>
+        <v>147.6</v>
       </c>
       <c r="F56" t="n">
-        <v>76.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="G56" t="n">
-        <v>28</v>
+        <v>33.3</v>
       </c>
       <c r="H56" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="I56" t="n">
         <v>0.93</v>
@@ -2492,16 +2492,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>98.09999999999999</v>
+        <v>123.5</v>
       </c>
       <c r="F57" t="n">
-        <v>60.9</v>
+        <v>76.7</v>
       </c>
       <c r="G57" t="n">
-        <v>18.3</v>
+        <v>23</v>
       </c>
       <c r="H57" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="I57" t="n">
         <v>0.93</v>

--- a/livrables/km_restants_sous_grande_vitesse.xlsx
+++ b/livrables/km_restants_sous_grande_vitesse.xlsx
@@ -789,10 +789,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C10" t="n">
-        <v>124.3</v>
+        <v>124.9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -800,22 +800,22 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>155.9</v>
+        <v>172.9</v>
       </c>
       <c r="F10" t="n">
-        <v>96.90000000000001</v>
+        <v>107.4</v>
       </c>
       <c r="G10" t="n">
-        <v>57.9</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I10" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="J10" t="n">
-        <v>2724</v>
+        <v>2752</v>
       </c>
     </row>
     <row r="11">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C11" t="n">
-        <v>124.3</v>
+        <v>124.9</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -836,22 +836,22 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>119.8</v>
+        <v>121.1</v>
       </c>
       <c r="F11" t="n">
-        <v>74.5</v>
+        <v>75.3</v>
       </c>
       <c r="G11" t="n">
-        <v>64.90000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="H11" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I11" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="J11" t="n">
-        <v>2724</v>
+        <v>2752</v>
       </c>
     </row>
     <row r="12">
@@ -861,10 +861,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C12" t="n">
-        <v>124.3</v>
+        <v>124.9</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -872,22 +872,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>213.6</v>
+        <v>247.2</v>
       </c>
       <c r="F12" t="n">
-        <v>132.7</v>
+        <v>153.6</v>
       </c>
       <c r="G12" t="n">
-        <v>48.3</v>
+        <v>55.9</v>
       </c>
       <c r="H12" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="I12" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="J12" t="n">
-        <v>2724</v>
+        <v>2752</v>
       </c>
     </row>
     <row r="13">
@@ -897,10 +897,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C13" t="n">
-        <v>124.3</v>
+        <v>124.9</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -908,22 +908,22 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>200.6</v>
+        <v>229.6</v>
       </c>
       <c r="F13" t="n">
-        <v>124.7</v>
+        <v>142.7</v>
       </c>
       <c r="G13" t="n">
-        <v>37.4</v>
+        <v>42.8</v>
       </c>
       <c r="H13" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="I13" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="J13" t="n">
-        <v>2724</v>
+        <v>2752</v>
       </c>
     </row>
     <row r="14">
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C30" t="n">
-        <v>124.3</v>
+        <v>124.9</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1520,22 +1520,22 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>93.2</v>
+        <v>99.2</v>
       </c>
       <c r="F30" t="n">
-        <v>57.9</v>
+        <v>61.6</v>
       </c>
       <c r="G30" t="n">
-        <v>34.6</v>
+        <v>36.8</v>
       </c>
       <c r="H30" t="n">
         <v>30</v>
       </c>
       <c r="I30" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="J30" t="n">
-        <v>1719</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="31">
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C31" t="n">
-        <v>124.3</v>
+        <v>124.9</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1556,22 +1556,22 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>105.3</v>
+        <v>106.3</v>
       </c>
       <c r="F31" t="n">
-        <v>65.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="G31" t="n">
-        <v>57</v>
+        <v>57.5</v>
       </c>
       <c r="H31" t="n">
         <v>17</v>
       </c>
       <c r="I31" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="J31" t="n">
-        <v>1719</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="32">
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C32" t="n">
-        <v>124.3</v>
+        <v>124.9</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1592,22 +1592,22 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>104.4</v>
+        <v>132.5</v>
       </c>
       <c r="F32" t="n">
-        <v>64.8</v>
+        <v>82.3</v>
       </c>
       <c r="G32" t="n">
-        <v>23.6</v>
+        <v>29.9</v>
       </c>
       <c r="H32" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I32" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="J32" t="n">
-        <v>1719</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="33">
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C33" t="n">
-        <v>124.3</v>
+        <v>124.9</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1628,22 +1628,22 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>105.2</v>
+        <v>110.8</v>
       </c>
       <c r="F33" t="n">
-        <v>65.40000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="G33" t="n">
-        <v>19.6</v>
+        <v>20.7</v>
       </c>
       <c r="H33" t="n">
         <v>62</v>
       </c>
       <c r="I33" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="J33" t="n">
-        <v>1719</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="34">
@@ -2229,10 +2229,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C50" t="n">
-        <v>124.3</v>
+        <v>124.9</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2252,10 +2252,10 @@
         <v>30</v>
       </c>
       <c r="I50" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="J50" t="n">
-        <v>1208</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="51">
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C51" t="n">
-        <v>124.3</v>
+        <v>124.9</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2288,10 +2288,10 @@
         <v>16</v>
       </c>
       <c r="I51" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="J51" t="n">
-        <v>1208</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="52">
@@ -2301,10 +2301,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C52" t="n">
-        <v>124.3</v>
+        <v>124.9</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -2312,22 +2312,22 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>72.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F52" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G52" t="n">
-        <v>16.4</v>
+        <v>17.8</v>
       </c>
       <c r="H52" t="n">
         <v>66</v>
       </c>
       <c r="I52" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="J52" t="n">
-        <v>1208</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="53">
@@ -2337,10 +2337,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C53" t="n">
-        <v>124.3</v>
+        <v>124.9</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2348,22 +2348,22 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>73.2</v>
+        <v>79.7</v>
       </c>
       <c r="F53" t="n">
-        <v>45.5</v>
+        <v>49.5</v>
       </c>
       <c r="G53" t="n">
-        <v>13.7</v>
+        <v>14.9</v>
       </c>
       <c r="H53" t="n">
         <v>67</v>
       </c>
       <c r="I53" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="J53" t="n">
-        <v>1208</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="54">
